--- a/positions/2026-05-22.xlsx
+++ b/positions/2026-05-22.xlsx
@@ -1,15 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stops" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Portfolio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Orders" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,16 +447,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>ANGL</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.67</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="3">
@@ -468,16 +467,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>BKLN</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.67</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="4">
@@ -488,16 +487,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PDBC</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.67</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="5">
@@ -508,16 +507,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REMX</t>
+          <t>EMB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.67</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +527,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>HYG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.67</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="7">
@@ -548,16 +547,656 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.67</v>
+        <v>8.289999999999999</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PDBC</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.77</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PFF</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>25.27</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SJNK</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.72</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>v1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>9.449999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMB</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>6.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PDBC</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.24</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PFF</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>26.71</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.03</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>VTIP</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>9.710000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EDV</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMB</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>5.63</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>JPST</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>26.38</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4.71</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>PDBC</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4.36</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VTIP</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>8.75</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +1210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,30 +1263,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ICLN</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>15.67</v>
       </c>
       <c r="E2" t="n">
-        <v>16.67</v>
+        <v>12.86</v>
       </c>
       <c r="F2" t="n">
-        <v>16.67</v>
+        <v>-2.81</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2.44</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -658,22 +1297,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="E3" t="n">
-        <v>16.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>16.67</v>
+        <v>0.71</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -681,7 +1320,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2.44</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -692,7 +1331,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -701,21 +1340,21 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67</v>
+        <v>5.77</v>
       </c>
       <c r="F4" t="n">
-        <v>16.67</v>
+        <v>-1.07</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>2.44</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="5">
@@ -726,22 +1365,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REMX</t>
+          <t>TLT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>16.67</v>
+        <v>4.7</v>
       </c>
       <c r="F5" t="n">
-        <v>16.67</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -749,7 +1388,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2.44</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -760,30 +1399,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>DBA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>12.38</v>
       </c>
       <c r="E6" t="n">
-        <v>16.67</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>16.67</v>
+        <v>-2.93</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7">
@@ -794,22 +1433,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sector2e</t>
+          <t>v2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SMH</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7.48</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>16.67</v>
+        <v>0.64</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -817,223 +1456,245 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>etf</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Weight%</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>12M ret%</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Stop%</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Stop price</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Margin%</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sector2e</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>SMH</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="E2" t="n">
-        <v>132</v>
-      </c>
-      <c r="F2" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>458.96</v>
-      </c>
-      <c r="H2" t="n">
-        <v>19.2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>sector2e</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>REMX</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="E3" t="n">
-        <v>155.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="G3" t="n">
-        <v>85.81</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>sector2e</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OIH</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="E4" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="F4" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="G4" t="n">
-        <v>385.08</v>
-      </c>
-      <c r="H4" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>sector2e</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ICLN</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="E5" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="H5" t="n">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>sector2e</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>PDBC</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="E6" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.4</v>
+      <c r="D8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>26.07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.71</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>v2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>VTIP</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.48</v>
+      </c>
+      <c r="E10" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DBA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="E11" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>JPST</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>24.23</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PDBC</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>v3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>VTIP</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>0.07000000000000001</v>
       </c>
     </row>
   </sheetData>
